--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Mistral-7B-Instruct-v0.3/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Mistral-7B-Instruct-v0.3/metrics_default_vs_aae.xlsx
@@ -420,22 +420,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.4782608695652174</v>
+        <v>0.4513274336283186</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C2">
-        <v>0.5070422535211268</v>
+        <v>0.4859154929577465</v>
       </c>
       <c r="D2">
-        <v>0.5600000000000001</v>
+        <v>0.584</v>
       </c>
       <c r="E2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>17</v>
